--- a/data/canary/valcan_pack_2026-04-12/_VALCAN_2026/40_CYBERSECURITY/valcanary_baseline_inventory_for_scans.xlsx
+++ b/data/canary/valcan_pack_2026-04-12/_VALCAN_2026/40_CYBERSECURITY/valcanary_baseline_inventory_for_scans.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>VALSITE-ALPHA</t>
+          <t>Site: Validation Alpha Site</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>VALSITE-ALPHA</t>
+          <t>Site: Validation Alpha Site</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>VALSITE-BRAVO</t>
+          <t>Site: Validation Bravo Site</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -643,7 +643,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>VALSITE-BRAVO</t>
+          <t>Site: Validation Bravo Site</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>VALSITE-CHARLIE</t>
+          <t>Site: Validation Charlie Site</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>VALSITE-CHARLIE</t>
+          <t>Site: Validation Charlie Site</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>VALSITE-DELTA</t>
+          <t>Site: Validation Delta Site</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>VALSITE-ECHO</t>
+          <t>Site: Validation Echo Site</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
